--- a/feedback_forms/004_prepaid_package_feedback_survey--feedback_forms.xlsx
+++ b/feedback_forms/004_prepaid_package_feedback_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -859,7 +859,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Explanation</t>
+          <t>Rating4 Label</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Why did you rate that way?</t>
+          <t>Rating4 Reason</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How likely are you to purchase again?</t>
+          <t>Rating5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Explanation</t>
+          <t>Rating5 Label</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Why did you rate that way?</t>
+          <t>Rating5 Reason</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -997,7 +997,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Explanation</t>
+          <t>Rating6 Label</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Why did you rate that way?</t>
+          <t>Rating6 Reason</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Explanation</t>
+          <t>Rating7 Label</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option':_1,_'value':_'highly_satisfied'}</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option': 1, 'value': 'Highly satisfied'}</t>
+          <t>Highly satisfied</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option':_2,_'value':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option': 2, 'value': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option':_3,_'value':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option': 3, 'value': 'Not satisfied'}</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option':_1,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option': 1, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_2,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 2, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
